--- a/data/trans_dic/P41C_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P41C_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dificultades para tener un embarazo</t>
+          <t>Población con dificultades para tener un embarazo (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>0,0; 5,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,45</t>
+          <t>0,0; 15,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,08</t>
+          <t>0,0; 8,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,63</t>
+          <t>1,0; 8,72</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 17,08</t>
+          <t>3,03; 17,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,95; 14,56</t>
+          <t>3,62; 14,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 13,05</t>
+          <t>4,63; 13,02</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,62</t>
+          <t>0,0; 27,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 12,62</t>
+          <t>1,8; 12,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 15,51</t>
+          <t>2,66; 14,45</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,44</t>
+          <t>0,0; 8,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,17</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,87</t>
+          <t>0,29; 3,73</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,69</t>
+          <t>0,99; 9,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,72</t>
+          <t>0,48; 4,59</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 13,98</t>
+          <t>3,16; 13,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,31; 10,08</t>
+          <t>3,33; 9,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,18; 10,07</t>
+          <t>4,15; 10,56</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,37</t>
+          <t>0,0; 4,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 7,05</t>
+          <t>1,07; 7,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 3,99</t>
+          <t>0,17; 3,91</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,04</t>
+          <t>1,15; 5,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,73</t>
+          <t>3,08; 5,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,81</t>
+          <t>2,23; 4,79</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dificultades para tener un embarazo</t>
+          <t>Población con dificultades para tener un embarazo (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1901</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3435</t>
+          <t>0; 3881</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3970</t>
+          <t>0; 3715</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 9581</t>
+          <t>0; 9572</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6286</t>
+          <t>0; 5024</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1195; 10733</t>
+          <t>1238; 10847</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2835; 12830</t>
+          <t>2273; 13100</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2977; 10974</t>
+          <t>2728; 10725</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7255; 19628</t>
+          <t>6962; 19586</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 13815</t>
+          <t>0; 18344</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1622; 8784</t>
+          <t>1250; 8965</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3804; 21186</t>
+          <t>3636; 19746</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2877</t>
+          <t>0; 4493</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3548</t>
+          <t>0; 3307</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>347; 4697</t>
+          <t>352; 4532</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1694</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>624; 5606</t>
+          <t>640; 5989</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>652; 6468</t>
+          <t>658; 6286</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3371; 14813</t>
+          <t>3349; 14398</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5074; 15459</t>
+          <t>5112; 15270</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10830; 26106</t>
+          <t>10770; 27389</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 16791</t>
+          <t>0; 17168</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1406; 9553</t>
+          <t>1451; 9642</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1130; 20771</t>
+          <t>888; 20343</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>10962; 44316</t>
+          <t>10115; 44032</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>21071; 39850</t>
+          <t>21409; 40083</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>32890; 75740</t>
+          <t>35191; 75386</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41C_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P41C_R-Provincia-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,88</t>
+          <t>0,0; 4,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,43</t>
+          <t>0,0; 14,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,06</t>
+          <t>0,0; 9,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,72</t>
+          <t>1,1; 8,65</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 17,44</t>
+          <t>2,82; 17,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 14,23</t>
+          <t>4,55; 15,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 13,02</t>
+          <t>4,99; 13,35</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,38</t>
+          <t>0,0; 24,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 12,88</t>
+          <t>2,19; 12,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 14,45</t>
+          <t>2,4; 14,91</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,5</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,73</t>
+          <t>0,24; 3,68</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,29</t>
+          <t>0,94; 9,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,59</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,16; 13,59</t>
+          <t>3,75; 15,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,33; 9,96</t>
+          <t>3,09; 9,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 10,56</t>
+          <t>3,96; 9,3</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,47</t>
+          <t>0,72; 7,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,11</t>
+          <t>1,1; 6,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,91</t>
+          <t>1,31; 5,62</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,01</t>
+          <t>2,64; 6,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,77</t>
+          <t>2,98; 5,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,79</t>
+          <t>3,19; 5,41</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1032</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3881</t>
+          <t>0; 3264</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3715</t>
+          <t>0; 3208</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4734</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 9572</t>
+          <t>0; 9437</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5024</t>
+          <t>0; 6292</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1238; 10847</t>
+          <t>1450; 11442</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6350</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>12917</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2273; 13100</t>
+          <t>2082; 12618</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2728; 10725</t>
+          <t>3521; 11690</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6962; 19586</t>
+          <t>7533; 20169</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>9380</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 18344</t>
+          <t>0; 18746</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1250; 8965</t>
+          <t>1697; 9354</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3636; 19746</t>
+          <t>3681; 22869</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>780</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1788</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4493</t>
+          <t>0; 4286</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3307</t>
+          <t>0; 3672</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>352; 4532</t>
+          <t>335; 5062</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2147</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>640; 5989</t>
+          <t>618; 6299</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>658; 6286</t>
+          <t>0; 6013</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17347</t>
+          <t>18900</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3349; 14398</t>
+          <t>4493; 18092</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5112; 15270</t>
+          <t>5529; 16455</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10770; 27389</t>
+          <t>11821; 27801</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>9427</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 17168</t>
+          <t>1183; 11682</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1451; 9642</t>
+          <t>1752; 10898</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>888; 20343</t>
+          <t>4241; 18137</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>26491</t>
+          <t>28556</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>29437</t>
+          <t>31769</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>55929</t>
+          <t>60325</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>10115; 44032</t>
+          <t>18345; 45806</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>21409; 40083</t>
+          <t>23090; 42269</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>35191; 75386</t>
+          <t>46801; 79563</t>
         </is>
       </c>
     </row>
